--- a/backend/storage/reports/xlsx/MoneyTrace_Analytics_Master_20260816.xlsx
+++ b/backend/storage/reports/xlsx/MoneyTrace_Analytics_Master_20260816.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-16 07:46 UTC</t>
+          <t>2026-08-16 17:57 UTC</t>
         </is>
       </c>
     </row>
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="8">
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9">
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10576027</v>
+        <v>10595027</v>
       </c>
     </row>
     <row r="12">
@@ -611,24 +611,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TXN_20260816_03824_3e523e</t>
+          <t>TXN_RING_CA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ACC1004</t>
+          <t>ACC_RING_C</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ACC64246741</t>
+          <t>ACC_RING_A</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>9317.129999999999</v>
+        <v>46000</v>
       </c>
       <c r="E2" t="n">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -637,31 +637,31 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-16 07:11</t>
+          <t>2026-08-16 17:33</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TXN_20260816_05062_cdc300</t>
+          <t>TXN_RING_BC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ACC75385116</t>
+          <t>ACC_RING_B</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ACC65809811</t>
+          <t>ACC_RING_C</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>818.63</v>
+        <v>48000</v>
       </c>
       <c r="E3" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -670,31 +670,31 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-16 07:06</t>
+          <t>2026-08-16 17:23</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TXN_20260816_03230_c196a8</t>
+          <t>TXN_RING_AB</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ACC1002</t>
+          <t>ACC_RING_A</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ACC43907404</t>
+          <t>ACC_RING_B</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4893.83</v>
+        <v>50000</v>
       </c>
       <c r="E4" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -703,31 +703,31 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-16 06:57</t>
+          <t>2026-08-16 17:13</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TXN_20260816_01548_84c68c</t>
+          <t>TXN_TRACE_HOP3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ACC36297523</t>
+          <t>ACC1003</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ACC82456100</t>
+          <t>ACC1004</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>5897.33</v>
+        <v>95000</v>
       </c>
       <c r="E5" t="n">
-        <v>17</v>
+        <v>100</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -736,31 +736,31 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:48</t>
+          <t>2026-08-16 16:18</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TXN_20260816_01202_0d3557</t>
+          <t>TXN_TRACE_HOP2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ACC91181015</t>
+          <t>ACC1002</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ACC97828025</t>
+          <t>ACC1003</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>19880.77</v>
+        <v>98000</v>
       </c>
       <c r="E6" t="n">
-        <v>26</v>
+        <v>100</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -769,31 +769,31 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-16 06:44</t>
+          <t>2026-08-16 16:03</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TXN_20260816_00830_46a093</t>
+          <t>TXN_TRACE_HOP1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ACC92107699</t>
+          <t>ACC1001</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ACC70103438</t>
+          <t>ACC1002</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>886.6900000000001</v>
+        <v>100000</v>
       </c>
       <c r="E7" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -802,19 +802,19 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:27</t>
+          <t>2026-08-16 15:53</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TXN_20260816_03509_9f670d</t>
+          <t>TXN_20260816_03824_3e523e</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ACC39727090</t>
+          <t>ACC1004</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>7959.29</v>
+        <v>9317.129999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -835,31 +835,31 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-08-16 06:26</t>
+          <t>2026-08-16 07:11</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TXN_20260816_03375_91dd5e</t>
+          <t>TXN_20260816_05062_cdc300</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ACC59760987</t>
+          <t>ACC75385116</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ACC11706152</t>
+          <t>ACC65809811</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>31566.7</v>
+        <v>818.63</v>
       </c>
       <c r="E9" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -868,31 +868,31 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-08-16 06:20</t>
+          <t>2026-08-16 07:06</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TXN_20260816_04685_9d5f2d</t>
+          <t>TXN_20260816_03230_c196a8</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ACC91181015</t>
+          <t>ACC1002</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ACC10897161</t>
+          <t>ACC43907404</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>32500.77</v>
+        <v>4893.83</v>
       </c>
       <c r="E10" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -901,31 +901,31 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-08-16 06:13</t>
+          <t>2026-08-16 06:57</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TXN_20260816_03315_1b51da</t>
+          <t>TXN_20260816_01548_84c68c</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ACC75311120</t>
+          <t>ACC36297523</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ACC75385116</t>
+          <t>ACC82456100</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17278.66</v>
+        <v>5897.33</v>
       </c>
       <c r="E11" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -934,31 +934,31 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-08-16 06:00</t>
+          <t>2026-08-16 06:48</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TXN_20260816_04089_d29996</t>
+          <t>TXN_20260816_01202_0d3557</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ACC40593754</t>
+          <t>ACC91181015</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ACC20858654</t>
+          <t>ACC97828025</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>38748.65</v>
+        <v>19880.77</v>
       </c>
       <c r="E12" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -967,31 +967,31 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-08-16 05:59</t>
+          <t>2026-08-16 06:44</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TXN_20260816_04642_c2da03</t>
+          <t>TXN_20260816_00830_46a093</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ACC16314613</t>
+          <t>ACC92107699</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ACC1001</t>
+          <t>ACC70103438</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>27885.78</v>
+        <v>886.6900000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1000,31 +1000,31 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-08-16 05:58</t>
+          <t>2026-08-16 06:27</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TXN_20260816_03644_f91e51</t>
+          <t>TXN_20260816_03509_9f670d</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ACC15373430</t>
+          <t>ACC39727090</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ACC75385116</t>
+          <t>ACC64246741</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>9304.450000000001</v>
+        <v>7959.29</v>
       </c>
       <c r="E14" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1033,31 +1033,31 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-08-16 05:47</t>
+          <t>2026-08-16 06:26</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TXN_20260816_02893_3862b4</t>
+          <t>TXN_20260816_03375_91dd5e</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ACC57224534</t>
+          <t>ACC59760987</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ACC50081547</t>
+          <t>ACC11706152</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>22578.25</v>
+        <v>31566.7</v>
       </c>
       <c r="E15" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1066,31 +1066,31 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-08-16 05:47</t>
+          <t>2026-08-16 06:20</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TXN_20260816_00144_1510a0</t>
+          <t>TXN_20260816_04685_9d5f2d</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ACC20858654</t>
+          <t>ACC91181015</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ACC75311120</t>
+          <t>ACC10897161</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>5316.41</v>
+        <v>32500.77</v>
       </c>
       <c r="E16" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1099,31 +1099,31 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-08-16 05:27</t>
+          <t>2026-08-16 06:13</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TXN_20260816_04822_c8e99a</t>
+          <t>TXN_20260816_03315_1b51da</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ACC1002</t>
+          <t>ACC75311120</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ACC36297523</t>
+          <t>ACC75385116</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>19599.6</v>
+        <v>17278.66</v>
       </c>
       <c r="E17" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1132,31 +1132,31 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-08-16 05:21</t>
+          <t>2026-08-16 06:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TXN_RING_CA</t>
+          <t>TXN_20260816_04089_d29996</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ACC_RING_C</t>
+          <t>ACC40593754</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ACC_RING_A</t>
+          <t>ACC20858654</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>46000</v>
+        <v>38748.65</v>
       </c>
       <c r="E18" t="n">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1165,31 +1165,31 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-08-16 05:21</t>
+          <t>2026-08-16 05:59</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TXN_CRITICAL_2291</t>
+          <t>TXN_20260816_04642_c2da03</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ACC50081547</t>
+          <t>ACC16314613</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ACC16314613</t>
+          <t>ACC1001</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>150000</v>
+        <v>27885.78</v>
       </c>
       <c r="E19" t="n">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1198,31 +1198,31 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-08-16 05:13</t>
+          <t>2026-08-16 05:58</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TXN_RING_BC</t>
+          <t>TXN_20260816_03644_f91e51</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ACC_RING_B</t>
+          <t>ACC15373430</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ACC_RING_C</t>
+          <t>ACC75385116</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>48000</v>
+        <v>9304.450000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1231,31 +1231,31 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-08-16 05:11</t>
+          <t>2026-08-16 05:47</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TXN_CRITICAL_4975</t>
+          <t>TXN_20260816_02893_3862b4</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ACC43907404</t>
+          <t>ACC57224534</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ACC16314613</t>
+          <t>ACC50081547</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>150000</v>
+        <v>22578.25</v>
       </c>
       <c r="E21" t="n">
-        <v>100</v>
+        <v>14</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1264,31 +1264,31 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-08-16 05:11</t>
+          <t>2026-08-16 05:47</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TXN_TRAVEL_DEL_137</t>
+          <t>TXN_20260816_00144_1510a0</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ACC65809811</t>
+          <t>ACC20858654</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ACC43249524</t>
+          <t>ACC75311120</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15000</v>
+        <v>5316.41</v>
       </c>
       <c r="E22" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1297,31 +1297,31 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-08-16 05:09</t>
+          <t>2026-08-16 05:27</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TXN_RAPID_4_114</t>
+          <t>TXN_20260816_04822_c8e99a</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ACC20858654</t>
+          <t>ACC1002</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ACC64246741</t>
+          <t>ACC36297523</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15000</v>
+        <v>19599.6</v>
       </c>
       <c r="E23" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1330,31 +1330,31 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-08-16 05:06</t>
+          <t>2026-08-16 05:21</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TXN_20260816_01589_34a1a8</t>
+          <t>TXN_CRITICAL_2291</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ACC36297523</t>
+          <t>ACC50081547</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ACC25189145</t>
+          <t>ACC16314613</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>26775.56</v>
+        <v>150000</v>
       </c>
       <c r="E24" t="n">
-        <v>23</v>
+        <v>100</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1363,31 +1363,31 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-08-16 05:05</t>
+          <t>2026-08-16 05:13</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TXN_RAPID_3_240</t>
+          <t>TXN_CRITICAL_4975</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ACC20858654</t>
+          <t>ACC43907404</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ACC11706152</t>
+          <t>ACC16314613</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15000</v>
+        <v>150000</v>
       </c>
       <c r="E25" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1396,31 +1396,31 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-08-16 05:05</t>
+          <t>2026-08-16 05:11</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TXN_RAPID_2_604</t>
+          <t>TXN_TRAVEL_DEL_137</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ACC20858654</t>
+          <t>ACC65809811</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ACC75385116</t>
+          <t>ACC43249524</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>15000</v>
       </c>
       <c r="E26" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1429,31 +1429,31 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-08-16 05:04</t>
+          <t>2026-08-16 05:09</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TXN_MULE_OUT_421</t>
+          <t>TXN_RAPID_4_114</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ACC59760987</t>
+          <t>ACC20858654</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ACC43249524</t>
+          <t>ACC64246741</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>95000</v>
+        <v>15000</v>
       </c>
       <c r="E27" t="n">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1462,28 +1462,31 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-08-16 05:04</t>
+          <t>2026-08-16 05:06</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>TXN_TRAVEL_MUM_781</t>
+          <t>TXN_20260816_01589_34a1a8</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ACC65809811</t>
+          <t>ACC36297523</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ACC16314613</t>
+          <t>ACC25189145</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>10000</v>
+        <v>26775.56</v>
+      </c>
+      <c r="E28" t="n">
+        <v>23</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1492,14 +1495,14 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-08-16 05:04</t>
+          <t>2026-08-16 05:05</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>TXN_RAPID_1_391</t>
+          <t>TXN_RAPID_3_240</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1509,7 +1512,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ACC15373430</t>
+          <t>ACC11706152</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1525,14 +1528,14 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-08-16 05:04</t>
+          <t>2026-08-16 05:05</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>TXN_RAPID_4_799</t>
+          <t>TXN_RAPID_2_604</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1542,7 +1545,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ACC64246741</t>
+          <t>ACC75385116</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1558,31 +1561,31 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-08-16 05:03</t>
+          <t>2026-08-16 05:04</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TXN_RAPID_3_986</t>
+          <t>TXN_MULE_OUT_421</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ACC20858654</t>
+          <t>ACC59760987</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ACC11706152</t>
+          <t>ACC43249524</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>15000</v>
+        <v>95000</v>
       </c>
       <c r="E31" t="n">
-        <v>25</v>
+        <v>90</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1591,31 +1594,28 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-08-16 05:03</t>
+          <t>2026-08-16 05:04</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>TXN_RAPID_2_632</t>
+          <t>TXN_TRAVEL_MUM_781</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ACC20858654</t>
+          <t>ACC65809811</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ACC75385116</t>
+          <t>ACC16314613</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>15000</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1624,14 +1624,14 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-08-16 05:02</t>
+          <t>2026-08-16 05:04</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TXN_RAPID_1_923</t>
+          <t>TXN_RAPID_1_391</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1648,7 +1648,7 @@
         <v>15000</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1657,31 +1657,31 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-08-16 05:01</t>
+          <t>2026-08-16 05:04</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>TXN_RING_AB</t>
+          <t>TXN_RAPID_4_799</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ACC_RING_A</t>
+          <t>ACC20858654</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ACC_RING_B</t>
+          <t>ACC64246741</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>50000</v>
+        <v>15000</v>
       </c>
       <c r="E34" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1690,31 +1690,31 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-08-16 05:01</t>
+          <t>2026-08-16 05:03</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>TXN_DRAIN_2385</t>
+          <t>TXN_RAPID_3_986</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ACC70103438</t>
+          <t>ACC20858654</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ACC43249524</t>
+          <t>ACC11706152</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>90000</v>
+        <v>15000</v>
       </c>
       <c r="E35" t="n">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1723,31 +1723,31 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-08-16 04:59</t>
+          <t>2026-08-16 05:03</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TXN_DRAIN_7223</t>
+          <t>TXN_RAPID_2_632</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ACC57224534</t>
+          <t>ACC20858654</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ACC43249524</t>
+          <t>ACC75385116</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>90000</v>
+        <v>15000</v>
       </c>
       <c r="E36" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1756,28 +1756,31 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-08-16 04:56</t>
+          <t>2026-08-16 05:02</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>TXN_MULE_IN_284</t>
+          <t>TXN_RAPID_1_923</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ACC16314613</t>
+          <t>ACC20858654</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ACC59760987</t>
+          <t>ACC15373430</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>100000</v>
+        <v>15000</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1786,31 +1789,31 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-08-16 04:44</t>
+          <t>2026-08-16 05:01</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>TXN_20260816_04681_4958e0</t>
+          <t>TXN_DRAIN_2385</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ACC50081547</t>
+          <t>ACC70103438</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ACC64246741</t>
+          <t>ACC43249524</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>29656.46</v>
+        <v>90000</v>
       </c>
       <c r="E38" t="n">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1819,31 +1822,31 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-08-16 04:34</t>
+          <t>2026-08-16 04:59</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>TXN_20260816_03501_07b435</t>
+          <t>TXN_DRAIN_7223</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ACC86445636</t>
+          <t>ACC57224534</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ACC74473089</t>
+          <t>ACC43249524</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>35723.31</v>
+        <v>90000</v>
       </c>
       <c r="E39" t="n">
-        <v>6</v>
+        <v>70</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -1852,31 +1855,28 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-08-16 04:30</t>
+          <t>2026-08-16 04:56</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>TXN_VERYLARGE_9496</t>
+          <t>TXN_MULE_IN_284</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ACC97828025</t>
+          <t>ACC16314613</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ACC20858654</t>
+          <t>ACC59760987</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>120000</v>
-      </c>
-      <c r="E40" t="n">
-        <v>70</v>
+        <v>100000</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -1885,31 +1885,31 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-08-16 04:29</t>
+          <t>2026-08-16 04:44</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>TXN_VERYLARGE_9360</t>
+          <t>TXN_20260816_04681_4958e0</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ACC92107699</t>
+          <t>ACC50081547</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ACC20858654</t>
+          <t>ACC64246741</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>120000</v>
+        <v>29656.46</v>
       </c>
       <c r="E41" t="n">
-        <v>70</v>
+        <v>24</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -1918,31 +1918,31 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-08-16 04:26</t>
+          <t>2026-08-16 04:34</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>TXN_20260816_00574_5c97b4</t>
+          <t>TXN_20260816_03501_07b435</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ACC_RING_A</t>
+          <t>ACC86445636</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ACC70103438</t>
+          <t>ACC74473089</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>39170.09</v>
+        <v>35723.31</v>
       </c>
       <c r="E42" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -1951,31 +1951,31 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-08-16 04:23</t>
+          <t>2026-08-16 04:30</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>TXN_20260816_03842_9a9210</t>
+          <t>TXN_VERYLARGE_9496</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ACC61076366</t>
+          <t>ACC97828025</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ACC43907404</t>
+          <t>ACC20858654</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>28952.92</v>
+        <v>120000</v>
       </c>
       <c r="E43" t="n">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -1984,19 +1984,19 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-08-16 04:21</t>
+          <t>2026-08-16 04:29</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>TXN_DEV_IPHONE_241</t>
+          <t>TXN_VERYLARGE_9360</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ACC74473089</t>
+          <t>ACC92107699</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2005,10 +2005,10 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>55000</v>
+        <v>120000</v>
       </c>
       <c r="E44" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -2017,31 +2017,31 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-08-16 04:14</t>
+          <t>2026-08-16 04:26</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>TXN_TRACE_HOP3</t>
+          <t>TXN_20260816_00574_5c97b4</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ACC1003</t>
+          <t>ACC_RING_A</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ACC1004</t>
+          <t>ACC70103438</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>95000</v>
+        <v>39170.09</v>
       </c>
       <c r="E45" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -2050,31 +2050,31 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-08-16 04:06</t>
+          <t>2026-08-16 04:23</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>TXN_TRACE_HOP2</t>
+          <t>TXN_20260816_03842_9a9210</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ACC1002</t>
+          <t>ACC61076366</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ACC1003</t>
+          <t>ACC43907404</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>98000</v>
+        <v>28952.92</v>
       </c>
       <c r="E46" t="n">
-        <v>100</v>
+        <v>22</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -2083,31 +2083,31 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-08-16 03:51</t>
+          <t>2026-08-16 04:21</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>TXN_20260816_03946_409ec7</t>
+          <t>TXN_DEV_IPHONE_241</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ACC66777666</t>
+          <t>ACC74473089</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ACC61076366</t>
+          <t>ACC20858654</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>6668.24</v>
+        <v>55000</v>
       </c>
       <c r="E47" t="n">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -2116,31 +2116,31 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-08-16 03:43</t>
+          <t>2026-08-16 04:14</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>TXN_TRACE_HOP1</t>
+          <t>TXN_20260816_03946_409ec7</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ACC1001</t>
+          <t>ACC66777666</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ACC1002</t>
+          <t>ACC61076366</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>100000</v>
+        <v>6668.24</v>
       </c>
       <c r="E48" t="n">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-08-16 03:41</t>
+          <t>2026-08-16 03:43</t>
         </is>
       </c>
     </row>
@@ -17110,7 +17110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G136"/>
+  <dimension ref="A1:G141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -17162,7 +17162,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ALT20260816054125768</t>
+          <t>ALT20260816175348433</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -17190,14 +17190,14 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-16 05:41</t>
+          <t>2026-08-16 17:53</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ALT20260816054125331</t>
+          <t>ALT20260816175348326</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -17225,14 +17225,14 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-16 05:41</t>
+          <t>2026-08-16 17:53</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ALT20260816054125694</t>
+          <t>ALT20260816175348335</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -17260,14 +17260,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-16 05:41</t>
+          <t>2026-08-16 17:53</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ALT20260816054125207</t>
+          <t>ALT20260816175348678</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -17295,14 +17295,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-16 05:41</t>
+          <t>2026-08-16 17:53</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ALT20260816054125190</t>
+          <t>ALT20260816175347938</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -17330,63 +17330,55 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-16 05:41</t>
+          <t>2026-08-16 17:53</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ALT20260816051407185</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>TXN_MULE_OUT_421</t>
-        </is>
-      </c>
+          <t>ALT20260816054125768</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Large Transaction, New Account Activity, Mule Account Activity</t>
+          <t>New Account Activity, Mule Account Activity</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FALSE_POSITIVE</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-16 05:14</t>
+          <t>2026-08-16 05:41</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ALT20260816051407126</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>TXN_DEV_IPHONE_241</t>
-        </is>
-      </c>
+          <t>ALT20260816054125331</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Large Transaction, New Account Activity, Device Change</t>
+          <t>New Account Activity, Mule Account Activity</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -17400,24 +17392,20 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-08-16 05:14</t>
+          <t>2026-08-16 05:41</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ALT20260816051406709</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>TXN_CRITICAL_2291</t>
-        </is>
-      </c>
+          <t>ALT20260816054125694</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Very Large Transaction, New Account Activity, Balance Drain</t>
+          <t>Large Transaction, New Account Activity, Balance Drain, Mule Account Activity</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -17435,32 +17423,28 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-08-16 05:14</t>
+          <t>2026-08-16 05:41</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ALT20260816051406520</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>TXN_DRAIN_2385</t>
-        </is>
-      </c>
+          <t>ALT20260816054125207</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Large Transaction, Balance Drain</t>
+          <t>Large Transaction, New Account Activity, Balance Drain, Mule Account Activity</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -17470,32 +17454,28 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-08-16 05:14</t>
+          <t>2026-08-16 05:41</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ALT20260816051406718</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>TXN_VERYLARGE_9496</t>
-        </is>
-      </c>
+          <t>ALT20260816054125190</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Very Large Transaction, New Account Activity</t>
+          <t>Large Transaction, New Account Activity</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -17505,37 +17485,37 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-08-16 05:14</t>
+          <t>2026-08-16 05:41</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ALT20260816051406734</t>
+          <t>ALT20260816051407185</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TXN_LARGE_9918</t>
+          <t>TXN_MULE_OUT_421</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Large Transaction, New Account Activity</t>
+          <t>Large Transaction, New Account Activity, Mule Account Activity</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>FALSE_POSITIVE</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -17547,25 +17527,25 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ALT20260816051149913</t>
+          <t>ALT20260816051407126</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TXN_CRITICAL_4975</t>
+          <t>TXN_DEV_IPHONE_241</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Very Large Transaction, New Account Activity, Balance Drain</t>
+          <t>Large Transaction, New Account Activity, Device Change</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -17575,32 +17555,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-08-16 05:11</t>
+          <t>2026-08-16 05:14</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ALT20260816051148721</t>
+          <t>ALT20260816051406709</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TXN_DRAIN_7223</t>
+          <t>TXN_CRITICAL_2291</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Large Transaction, Balance Drain</t>
+          <t>Very Large Transaction, New Account Activity, Balance Drain</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -17610,24 +17590,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-08-16 05:11</t>
+          <t>2026-08-16 05:14</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ALT20260816051148953</t>
+          <t>ALT20260816051406520</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TXN_VERYLARGE_9360</t>
+          <t>TXN_DRAIN_2385</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Very Large Transaction, New Account Activity</t>
+          <t>Large Transaction, Balance Drain</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -17645,32 +17625,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-08-16 05:11</t>
+          <t>2026-08-16 05:14</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ALT20260816051148545</t>
+          <t>ALT20260816051406718</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TXN_LARGE_1699</t>
+          <t>TXN_VERYLARGE_9496</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Large Transaction, New Account Activity</t>
+          <t>Very Large Transaction, New Account Activity</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -17680,133 +17660,133 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-08-16 05:11</t>
+          <t>2026-08-16 05:14</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ALT20260815235543_028_59d5</t>
+          <t>ALT20260816051406734</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>TXN_20260815_00028_0d8d89</t>
+          <t>TXN_LARGE_9918</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Rapid Transfers</t>
+          <t>Large Transaction, New Account Activity</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>94</v>
+        <v>50</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>UNDER_REVIEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-08-15 23:55</t>
+          <t>2026-08-16 05:14</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ALT20260815182731_097_b7ea</t>
+          <t>ALT20260816051149913</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>TXN_20260815_01960_34c116</t>
+          <t>TXN_CRITICAL_4975</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Impossible Travel, New Account Activity</t>
+          <t>Very Large Transaction, New Account Activity, Balance Drain</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>73</v>
+        <v>100</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>UNDER_REVIEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-08-15 18:27</t>
+          <t>2026-08-16 05:11</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ALT20260815160630_048_b39c</t>
+          <t>ALT20260816051148721</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>TXN_20260815_00048_9479ec</t>
+          <t>TXN_DRAIN_7223</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Rapid Transfers, Balance Drain, New Account Activity</t>
+          <t>Large Transaction, Balance Drain</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>UNDER_REVIEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-08-15 16:06</t>
+          <t>2026-08-16 05:11</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ALT20260815095130_061_5377</t>
+          <t>ALT20260816051148953</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>TXN_20260815_00520_673135</t>
+          <t>TXN_VERYLARGE_9360</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Rapid Transfers</t>
+          <t>Very Large Transaction, New Account Activity</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -17820,32 +17800,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-08-15 09:51</t>
+          <t>2026-08-16 05:11</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ALT20260815045630_029_8466</t>
+          <t>ALT20260816051148545</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>TXN_20260815_00029_caa32f</t>
+          <t>TXN_LARGE_1699</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Large Transaction</t>
+          <t>Large Transaction, New Account Activity</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -17855,32 +17835,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-08-15 04:56</t>
+          <t>2026-08-16 05:11</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ALT20260815032849_013_4ed0</t>
+          <t>ALT20260815235543_028_59d5</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>TXN_20260815_00013_c5c8c5</t>
+          <t>TXN_20260815_00028_0d8d89</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New Account Activity</t>
+          <t>Rapid Transfers</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -17890,32 +17870,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-08-15 03:28</t>
+          <t>2026-08-15 23:55</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ALT20260814172622_087_ea68</t>
+          <t>ALT20260815182731_097_b7ea</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>TXN_20260814_01560_b52a36</t>
+          <t>TXN_20260815_01960_34c116</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Rapid Transfers</t>
+          <t>Impossible Travel, New Account Activity</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -17925,28 +17905,28 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-08-14 17:26</t>
+          <t>2026-08-15 18:27</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ALT20260814102124_035_f443</t>
+          <t>ALT20260815160630_048_b39c</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>TXN_20260814_00035_2f04bf</t>
+          <t>TXN_20260815_00048_9479ec</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Device Change</t>
+          <t>Rapid Transfers, Balance Drain, New Account Activity</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -17960,28 +17940,28 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-08-14 10:21</t>
+          <t>2026-08-15 16:06</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ALT20260813093505_106_c4c9</t>
+          <t>ALT20260815095130_061_5377</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>TXN_20260813_02320_8196ec</t>
+          <t>TXN_20260815_00520_673135</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Balance Drain, Impossible Travel</t>
+          <t>Rapid Transfers</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -17990,59 +17970,59 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>UNDER_REVIEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-08-13 09:35</t>
+          <t>2026-08-15 09:51</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ALT20260813084437_010_dde9</t>
+          <t>ALT20260815045630_029_8466</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>TXN_20260813_00010_bcb7cc</t>
+          <t>TXN_20260815_00029_caa32f</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Balance Drain</t>
+          <t>Large Transaction</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>UNDER_REVIEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-08-13 08:44</t>
+          <t>2026-08-15 04:56</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ALT20260813041524_119_48fa</t>
+          <t>ALT20260815032849_013_4ed0</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>TXN_20260813_02840_c8ad13</t>
+          <t>TXN_20260815_00013_c5c8c5</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -18051,112 +18031,112 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>UNDER_REVIEW</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-08-13 04:15</t>
+          <t>2026-08-15 03:28</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ALT20260812233300_057_bef8</t>
+          <t>ALT20260814172622_087_ea68</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>TXN_20260812_00360_27dd5c</t>
+          <t>TXN_20260814_01560_b52a36</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Mule Account Activity</t>
+          <t>Rapid Transfers</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>UNDER_REVIEW</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-08-12 23:33</t>
+          <t>2026-08-14 17:26</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ALT20260812210151_045_73ca</t>
+          <t>ALT20260814102124_035_f443</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>TXN_20260812_00045_05c815</t>
+          <t>TXN_20260814_00035_2f04bf</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Large Transaction, Balance Drain, Very Large Transaction</t>
+          <t>Device Change</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>UNDER_REVIEW</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-08-12 21:01</t>
+          <t>2026-08-14 10:21</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ALT20260812135102_049_ac3f</t>
+          <t>ALT20260813093505_106_c4c9</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>TXN_20260812_00049_93614e</t>
+          <t>TXN_20260813_02320_8196ec</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Mule Account Activity</t>
+          <t>Balance Drain, Impossible Travel</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -18165,33 +18145,33 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>UNDER_REVIEW</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-08-12 13:51</t>
+          <t>2026-08-13 09:35</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ALT20260812065543_016_f65b</t>
+          <t>ALT20260813084437_010_dde9</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>TXN_20260812_00016_6b2347</t>
+          <t>TXN_20260813_00010_bcb7cc</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New Account Activity, Very Large Transaction</t>
+          <t>Balance Drain</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -18200,37 +18180,37 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>UNDER_REVIEW</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-08-12 06:55</t>
+          <t>2026-08-13 08:44</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ALT20260812061803_009_f9e5</t>
+          <t>ALT20260813041524_119_48fa</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>TXN_20260812_00009_4c1f47</t>
+          <t>TXN_20260813_02840_c8ad13</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Rapid Transfers</t>
+          <t>New Account Activity</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -18240,94 +18220,94 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-08-12 06:18</t>
+          <t>2026-08-13 04:15</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ALT20260812041708_069_1539</t>
+          <t>ALT20260812233300_057_bef8</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>TXN_20260812_00840_737131</t>
+          <t>TXN_20260812_00360_27dd5c</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Mule Account Activity, Device Change</t>
+          <t>Mule Account Activity</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>UNDER_REVIEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-08-12 04:17</t>
+          <t>2026-08-12 23:33</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ALT20260811191550_098_e056</t>
+          <t>ALT20260812210151_045_73ca</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>TXN_20260811_02000_c2a159</t>
+          <t>TXN_20260812_00045_05c815</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Balance Drain</t>
+          <t>Large Transaction, Balance Drain, Very Large Transaction</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>UNDER_REVIEW</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-08-11 19:15</t>
+          <t>2026-08-12 21:01</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ALT20260810145643_111_26ba</t>
+          <t>ALT20260812135102_049_ac3f</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>TXN_20260810_02520_ebc2b8</t>
+          <t>TXN_20260812_00049_93614e</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Rapid Transfers</t>
+          <t>Mule Account Activity</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -18345,54 +18325,54 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-08-10 14:56</t>
+          <t>2026-08-12 13:51</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ALT20260810115907_020_ff98</t>
+          <t>ALT20260812065543_016_f65b</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>TXN_20260810_00020_8d4583</t>
+          <t>TXN_20260812_00016_6b2347</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Large Transaction</t>
+          <t>New Account Activity, Very Large Transaction</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-08-10 11:59</t>
+          <t>2026-08-12 06:55</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ALT20260810053942_102_4517</t>
+          <t>ALT20260812061803_009_f9e5</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>TXN_20260810_02160_e0f897</t>
+          <t>TXN_20260812_00009_4c1f47</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -18401,42 +18381,42 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>UNDER_REVIEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-08-10 05:39</t>
+          <t>2026-08-12 06:18</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ALT20260808104410_000_e341</t>
+          <t>ALT20260812041708_069_1539</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>TXN_20260808_00000_bc5947</t>
+          <t>TXN_20260812_00840_737131</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New Account Activity</t>
+          <t>Mule Account Activity, Device Change</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -18450,28 +18430,28 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-08-08 10:44</t>
+          <t>2026-08-12 04:17</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ALT20260808102515_030_3b2d</t>
+          <t>ALT20260811191550_098_e056</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>TXN_20260808_00030_a328a5</t>
+          <t>TXN_20260811_02000_c2a159</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Very Large Transaction</t>
+          <t>Balance Drain</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -18480,68 +18460,68 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>UNDER_REVIEW</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-08-08 10:25</t>
+          <t>2026-08-11 19:15</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ALT20260808064720_074_1358</t>
+          <t>ALT20260810145643_111_26ba</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>TXN_20260808_01040_684244</t>
+          <t>TXN_20260810_02520_ebc2b8</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Mule Account Activity, Rapid Transfers</t>
+          <t>Rapid Transfers</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>UNDER_REVIEW</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-08-08 06:47</t>
+          <t>2026-08-10 14:56</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ALT20260808020130_024_2469</t>
+          <t>ALT20260810115907_020_ff98</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>TXN_20260808_00024_85fa3e</t>
+          <t>TXN_20260810_00020_8d4583</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Rapid Transfers</t>
+          <t>Large Transaction</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -18550,33 +18530,33 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-08-08 02:01</t>
+          <t>2026-08-10 11:59</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ALT20260808015122_014_d3ea</t>
+          <t>ALT20260810053942_102_4517</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>TXN_20260808_00014_9d272f</t>
+          <t>TXN_20260810_02160_e0f897</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Large Transaction</t>
+          <t>Rapid Transfers</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -18585,33 +18565,33 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>UNDER_REVIEW</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-08-08 01:51</t>
+          <t>2026-08-10 05:39</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ALT20260807213743_003_cbce</t>
+          <t>ALT20260808104410_000_e341</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>TXN_20260807_00003_b18727</t>
+          <t>TXN_20260808_00000_bc5947</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Very Large Transaction, Impossible Travel, Mule Account Activity</t>
+          <t>New Account Activity</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -18625,28 +18605,28 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-08-07 21:37</t>
+          <t>2026-08-08 10:44</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ALT20260807202547_001_1ca8</t>
+          <t>ALT20260808102515_030_3b2d</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>TXN_20260807_00001_01e4f4</t>
+          <t>TXN_20260808_00030_a328a5</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Mule Account Activity, Large Transaction, Very Large Transaction</t>
+          <t>Very Large Transaction</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -18660,32 +18640,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-08-07 20:25</t>
+          <t>2026-08-08 10:25</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ALT20260806214646_005_f777</t>
+          <t>ALT20260808064720_074_1358</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>TXN_20260806_00005_597751</t>
+          <t>TXN_20260808_01040_684244</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New Account Activity</t>
+          <t>Mule Account Activity, Rapid Transfers</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -18695,28 +18675,28 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-08-06 21:46</t>
+          <t>2026-08-08 06:47</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ALT20260806211444_053_bd7c</t>
+          <t>ALT20260808020130_024_2469</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>TXN_20260806_00200_cedddf</t>
+          <t>TXN_20260808_00024_85fa3e</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Impossible Travel</t>
+          <t>Rapid Transfers</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -18730,28 +18710,28 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-08-06 21:14</t>
+          <t>2026-08-08 02:01</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ALT20260806134035_056_3a70</t>
+          <t>ALT20260808015122_014_d3ea</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>TXN_20260806_00320_bad216</t>
+          <t>TXN_20260808_00014_9d272f</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Impossible Travel</t>
+          <t>Large Transaction</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -18765,32 +18745,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-08-06 13:40</t>
+          <t>2026-08-08 01:51</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ALT20260806092130_041_90cd</t>
+          <t>ALT20260807213743_003_cbce</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>TXN_20260806_00041_cf21d7</t>
+          <t>TXN_20260807_00003_b18727</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Rapid Transfers, New Account Activity, Large Transaction</t>
+          <t>Very Large Transaction, Impossible Travel, Mule Account Activity</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -18800,24 +18780,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-08-06 09:21</t>
+          <t>2026-08-07 21:37</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ALT20260805224454_072_1614</t>
+          <t>ALT20260807202547_001_1ca8</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>TXN_20260805_00960_346624</t>
+          <t>TXN_20260807_00001_01e4f4</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Impossible Travel, Rapid Transfers, Balance Drain</t>
+          <t>Mule Account Activity, Large Transaction, Very Large Transaction</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -18835,28 +18815,28 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-08-05 22:44</t>
+          <t>2026-08-07 20:25</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ALT20260805194907_027_5a9b</t>
+          <t>ALT20260806214646_005_f777</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>TXN_20260805_00027_b6f4d8</t>
+          <t>TXN_20260806_00005_597751</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Rapid Transfers, Balance Drain</t>
+          <t>New Account Activity</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -18870,63 +18850,63 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-08-05 19:49</t>
+          <t>2026-08-06 21:46</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ALT20260805194432_091_01dc</t>
+          <t>ALT20260806211444_053_bd7c</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>TXN_20260805_01720_5896f6</t>
+          <t>TXN_20260806_00200_cedddf</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Device Change, Rapid Transfers</t>
+          <t>Impossible Travel</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>95</v>
+        <v>68</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>UNDER_REVIEW</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-08-05 19:44</t>
+          <t>2026-08-06 21:14</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ALT20260805055148_078_264e</t>
+          <t>ALT20260806134035_056_3a70</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>TXN_20260805_01200_e97277</t>
+          <t>TXN_20260806_00320_bad216</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Balance Drain</t>
+          <t>Impossible Travel</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -18935,29 +18915,29 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-08-05 05:51</t>
+          <t>2026-08-06 13:40</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ALT20260805050335_079_77b0</t>
+          <t>ALT20260806092130_041_90cd</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>TXN_20260805_01240_d6a09a</t>
+          <t>TXN_20260806_00041_cf21d7</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Very Large Transaction, Device Change, Large Transaction</t>
+          <t>Rapid Transfers, New Account Activity, Large Transaction</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -18975,28 +18955,28 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-08-05 05:03</t>
+          <t>2026-08-06 09:21</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ALT20260805045936_110_d362</t>
+          <t>ALT20260805224454_072_1614</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>TXN_20260805_02480_a85fd4</t>
+          <t>TXN_20260805_00960_346624</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>New Account Activity, Rapid Transfers, Mule Account Activity</t>
+          <t>Impossible Travel, Rapid Transfers, Balance Drain</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -19005,33 +18985,33 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-08-05 04:59</t>
+          <t>2026-08-05 22:44</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ALT20260805001738_042_ee87</t>
+          <t>ALT20260805194907_027_5a9b</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>TXN_20260805_00042_6bb61b</t>
+          <t>TXN_20260805_00027_b6f4d8</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Mule Account Activity</t>
+          <t>Rapid Transfers, Balance Drain</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -19045,28 +19025,28 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-08-05 00:17</t>
+          <t>2026-08-05 19:49</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ALT20260804195552_086_a9cc</t>
+          <t>ALT20260805194432_091_01dc</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>TXN_20260804_01520_88df22</t>
+          <t>TXN_20260805_01720_5896f6</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Mule Account Activity, Balance Drain, Large Transaction</t>
+          <t>Device Change, Rapid Transfers</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -19075,33 +19055,33 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>UNDER_REVIEW</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-08-04 19:55</t>
+          <t>2026-08-05 19:44</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ALT20260804192134_038_1542</t>
+          <t>ALT20260805055148_078_264e</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>TXN_20260804_00038_6a2940</t>
+          <t>TXN_20260805_01200_e97277</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Impossible Travel</t>
+          <t>Balance Drain</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -19110,33 +19090,33 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>UNDER_REVIEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-08-04 19:21</t>
+          <t>2026-08-05 05:51</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ALT20260804040715_015_49ff</t>
+          <t>ALT20260805050335_079_77b0</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>TXN_20260804_00015_5d7e6b</t>
+          <t>TXN_20260805_01240_d6a09a</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Rapid Transfers, Device Change</t>
+          <t>Very Large Transaction, Device Change, Large Transaction</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -19145,33 +19125,33 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>UNDER_REVIEW</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-08-04 04:07</t>
+          <t>2026-08-05 05:03</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ALT20260804011605_070_0393</t>
+          <t>ALT20260805045936_110_d362</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>TXN_20260804_00880_6095d8</t>
+          <t>TXN_20260805_02480_a85fd4</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Rapid Transfers</t>
+          <t>New Account Activity, Rapid Transfers, Mule Account Activity</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -19185,28 +19165,28 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-08-04 01:16</t>
+          <t>2026-08-05 04:59</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ALT20260803184415_114_6bb4</t>
+          <t>ALT20260805001738_042_ee87</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>TXN_20260803_02640_4b64d4</t>
+          <t>TXN_20260805_00042_6bb61b</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Device Change, Large Transaction</t>
+          <t>Mule Account Activity</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -19215,33 +19195,33 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>UNDER_REVIEW</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-08-03 18:44</t>
+          <t>2026-08-05 00:17</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ALT20260803122926_052_32b3</t>
+          <t>ALT20260804195552_086_a9cc</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>TXN_20260803_00160_99ca0c</t>
+          <t>TXN_20260804_01520_88df22</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Large Transaction</t>
+          <t>Mule Account Activity, Balance Drain, Large Transaction</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -19250,33 +19230,33 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-08-03 12:29</t>
+          <t>2026-08-04 19:55</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ALT20260803045202_007_ddbb</t>
+          <t>ALT20260804192134_038_1542</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>TXN_20260803_00007_f0d7b8</t>
+          <t>TXN_20260804_00038_6a2940</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Large Transaction</t>
+          <t>Impossible Travel</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -19285,68 +19265,68 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>UNDER_REVIEW</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-08-03 04:52</t>
+          <t>2026-08-04 19:21</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ALT20260803005407_008_da96</t>
+          <t>ALT20260804040715_015_49ff</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>TXN_20260803_00008_016e45</t>
+          <t>TXN_20260804_00015_5d7e6b</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>New Account Activity, Very Large Transaction</t>
+          <t>Rapid Transfers, Device Change</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>UNDER_REVIEW</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-08-03 00:54</t>
+          <t>2026-08-04 04:07</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ALT20260802102935_006_9a3d</t>
+          <t>ALT20260804011605_070_0393</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>TXN_20260802_00006_a05410</t>
+          <t>TXN_20260804_00880_6095d8</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Mule Account Activity, Rapid Transfers</t>
+          <t>Rapid Transfers</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -19355,103 +19335,103 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-08-02 10:29</t>
+          <t>2026-08-04 01:16</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ALT20260802074732_109_fbf3</t>
+          <t>ALT20260803184415_114_6bb4</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>TXN_20260802_02440_e9faf2</t>
+          <t>TXN_20260803_02640_4b64d4</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Mule Account Activity, Balance Drain</t>
+          <t>Device Change, Large Transaction</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-08-02 07:47</t>
+          <t>2026-08-03 18:44</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ALT20260802044208_031_c064</t>
+          <t>ALT20260803122926_052_32b3</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>TXN_20260802_00031_6b76cb</t>
+          <t>TXN_20260803_00160_99ca0c</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Mule Account Activity, Very Large Transaction, Large Transaction</t>
+          <t>Large Transaction</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>UNDER_REVIEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-08-02 04:42</t>
+          <t>2026-08-03 12:29</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ALT20260802014229_047_7255</t>
+          <t>ALT20260803045202_007_ddbb</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>TXN_20260802_00047_23dc59</t>
+          <t>TXN_20260803_00007_f0d7b8</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Impossible Travel, Balance Drain, Rapid Transfers</t>
+          <t>Large Transaction</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -19460,37 +19440,37 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-08-02 01:42</t>
+          <t>2026-08-03 04:52</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ALT20260802004753_017_4bea</t>
+          <t>ALT20260803005407_008_da96</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>TXN_20260802_00017_959970</t>
+          <t>TXN_20260803_00008_016e45</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>New Account Activity, Rapid Transfers, Impossible Travel</t>
+          <t>New Account Activity, Very Large Transaction</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -19500,67 +19480,67 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-08-02 00:47</t>
+          <t>2026-08-03 00:54</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ALT20260801111233_084_ca2c</t>
+          <t>ALT20260802102935_006_9a3d</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>TXN_20260801_01440_095d7e</t>
+          <t>TXN_20260802_00006_a05410</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Mule Account Activity, Device Change, Balance Drain</t>
+          <t>Mule Account Activity, Rapid Transfers</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-08-01 11:12</t>
+          <t>2026-08-02 10:29</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ALT20260801100011_103_ed49</t>
+          <t>ALT20260802074732_109_fbf3</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>TXN_20260801_02200_6b150d</t>
+          <t>TXN_20260802_02440_e9faf2</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>New Account Activity, Impossible Travel</t>
+          <t>Mule Account Activity, Balance Drain</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -19570,133 +19550,133 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-08-01 10:00</t>
+          <t>2026-08-02 07:47</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ALT20260801090027_040_8e9b</t>
+          <t>ALT20260802044208_031_c064</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>TXN_20260801_00040_efa568</t>
+          <t>TXN_20260802_00031_6b76cb</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>New Account Activity, Large Transaction, Balance Drain</t>
+          <t>Mule Account Activity, Very Large Transaction, Large Transaction</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>UNDER_REVIEW</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-08-01 09:00</t>
+          <t>2026-08-02 04:42</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ALT20260801061833_092_8738</t>
+          <t>ALT20260802014229_047_7255</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>TXN_20260801_01760_1754dc</t>
+          <t>TXN_20260802_00047_23dc59</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Very Large Transaction, Rapid Transfers</t>
+          <t>Impossible Travel, Balance Drain, Rapid Transfers</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>UNDER_REVIEW</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-08-01 06:18</t>
+          <t>2026-08-02 01:42</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ALT20260731184402_021_ad25</t>
+          <t>ALT20260802004753_017_4bea</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>TXN_20260731_00021_9ac21e</t>
+          <t>TXN_20260802_00017_959970</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Impossible Travel, Balance Drain, Rapid Transfers</t>
+          <t>New Account Activity, Rapid Transfers, Impossible Travel</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>UNDER_REVIEW</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-07-31 18:44</t>
+          <t>2026-08-02 00:47</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ALT20260731142844_037_b963</t>
+          <t>ALT20260801111233_084_ca2c</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>TXN_20260731_00037_0d0bf8</t>
+          <t>TXN_20260801_01440_095d7e</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Impossible Travel, Mule Account Activity</t>
+          <t>Mule Account Activity, Device Change, Balance Drain</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -19710,28 +19690,28 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-07-31 14:28</t>
+          <t>2026-08-01 11:12</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ALT20260731081025_066_a464</t>
+          <t>ALT20260801100011_103_ed49</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>TXN_20260731_00720_c9daae</t>
+          <t>TXN_20260801_02200_6b150d</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Impossible Travel, Rapid Transfers</t>
+          <t>New Account Activity, Impossible Travel</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -19740,33 +19720,33 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-07-31 08:10</t>
+          <t>2026-08-01 10:00</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ALT20260731074724_108_2d7d</t>
+          <t>ALT20260801090027_040_8e9b</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>TXN_20260731_02400_bf7da3</t>
+          <t>TXN_20260801_00040_efa568</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>New Account Activity, Impossible Travel, Very Large Transaction</t>
+          <t>New Account Activity, Large Transaction, Balance Drain</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -19775,33 +19755,33 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-07-31 07:47</t>
+          <t>2026-08-01 09:00</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ALT20260731012552_117_1a83</t>
+          <t>ALT20260801061833_092_8738</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>TXN_20260731_02760_72069e</t>
+          <t>TXN_20260801_01760_1754dc</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Large Transaction, Balance Drain</t>
+          <t>Very Large Transaction, Rapid Transfers</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -19810,107 +19790,107 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>UNDER_REVIEW</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-07-31 01:25</t>
+          <t>2026-08-01 06:18</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ALT20260729184758_094_7e44</t>
+          <t>ALT20260731184402_021_ad25</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>TXN_20260729_01840_8fdccc</t>
+          <t>TXN_20260731_00021_9ac21e</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Rapid Transfers, New Account Activity</t>
+          <t>Impossible Travel, Balance Drain, Rapid Transfers</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-07-29 18:47</t>
+          <t>2026-07-31 18:44</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ALT20260729060450_011_95cc</t>
+          <t>ALT20260731142844_037_b963</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>TXN_20260729_00011_2115c3</t>
+          <t>TXN_20260731_00037_0d0bf8</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Rapid Transfers, Mule Account Activity, New Account Activity</t>
+          <t>Impossible Travel, Mule Account Activity</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>UNDER_REVIEW</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-07-29 06:04</t>
+          <t>2026-07-31 14:28</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ALT20260729042123_063_64c1</t>
+          <t>ALT20260731081025_066_a464</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>TXN_20260729_00600_7c379d</t>
+          <t>TXN_20260731_00720_c9daae</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Device Change, New Account Activity, Impossible Travel</t>
+          <t>Impossible Travel, Rapid Transfers</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -19920,24 +19900,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-07-29 04:21</t>
+          <t>2026-07-31 08:10</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ALT20260728140703_004_93a5</t>
+          <t>ALT20260731074724_108_2d7d</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>TXN_20260728_00004_8c7a80</t>
+          <t>TXN_20260731_02400_bf7da3</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Mule Account Activity, Large Transaction, Very Large Transaction</t>
+          <t>New Account Activity, Impossible Travel, Very Large Transaction</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -19955,28 +19935,28 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-07-28 14:07</t>
+          <t>2026-07-31 07:47</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ALT20260728133508_077_b62b</t>
+          <t>ALT20260731012552_117_1a83</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>TXN_20260728_01160_13fa0e</t>
+          <t>TXN_20260731_02760_72069e</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Very Large Transaction</t>
+          <t>Large Transaction, Balance Drain</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -19985,33 +19965,33 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-07-28 13:35</t>
+          <t>2026-07-31 01:25</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ALT20260728102855_062_bd20</t>
+          <t>ALT20260729184758_094_7e44</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>TXN_20260728_00560_3411dd</t>
+          <t>TXN_20260729_01840_8fdccc</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Mule Account Activity, Impossible Travel, Large Transaction</t>
+          <t>Rapid Transfers, New Account Activity</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -20025,28 +20005,28 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-07-28 10:28</t>
+          <t>2026-07-29 18:47</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ALT20260727225056_060_80dc</t>
+          <t>ALT20260729060450_011_95cc</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>TXN_20260727_00480_ca06c1</t>
+          <t>TXN_20260729_00011_2115c3</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Very Large Transaction, Mule Account Activity, New Account Activity</t>
+          <t>Rapid Transfers, Mule Account Activity, New Account Activity</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -20055,68 +20035,68 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>UNDER_REVIEW</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-07-27 22:50</t>
+          <t>2026-07-29 06:04</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ALT20260727182736_067_49b1</t>
+          <t>ALT20260729042123_063_64c1</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>TXN_20260727_00760_3b473f</t>
+          <t>TXN_20260729_00600_7c379d</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Balance Drain</t>
+          <t>Device Change, New Account Activity, Impossible Travel</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>UNDER_REVIEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-07-27 18:27</t>
+          <t>2026-07-29 04:21</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ALT20260727111050_101_96a7</t>
+          <t>ALT20260728140703_004_93a5</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>TXN_20260727_02120_bb6ab9</t>
+          <t>TXN_20260728_00004_8c7a80</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Impossible Travel, Balance Drain, Very Large Transaction</t>
+          <t>Mule Account Activity, Large Transaction, Very Large Transaction</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -20125,72 +20105,72 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-07-27 11:10</t>
+          <t>2026-07-28 14:07</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ALT20260727110706_099_05a8</t>
+          <t>ALT20260728133508_077_b62b</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>TXN_20260727_02040_7c6879</t>
+          <t>TXN_20260728_01160_13fa0e</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Balance Drain</t>
+          <t>Very Large Transaction</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-07-27 11:07</t>
+          <t>2026-07-28 13:35</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ALT20260726230032_054_4584</t>
+          <t>ALT20260728102855_062_bd20</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>TXN_20260726_00240_31760a</t>
+          <t>TXN_20260728_00560_3411dd</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Device Change, Mule Account Activity, Impossible Travel</t>
+          <t>Mule Account Activity, Impossible Travel, Large Transaction</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -20200,28 +20180,28 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-07-26 23:00</t>
+          <t>2026-07-28 10:28</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ALT20260726170102_107_f3bc</t>
+          <t>ALT20260727225056_060_80dc</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>TXN_20260726_02360_eb7295</t>
+          <t>TXN_20260727_00480_ca06c1</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Impossible Travel, Device Change</t>
+          <t>Very Large Transaction, Mule Account Activity, New Account Activity</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -20230,33 +20210,33 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-07-26 17:01</t>
+          <t>2026-07-27 22:50</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ALT20260726161233_019_5213</t>
+          <t>ALT20260727182736_067_49b1</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>TXN_20260726_00019_4433ff</t>
+          <t>TXN_20260727_00760_3b473f</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Rapid Transfers, Balance Drain, Very Large Transaction</t>
+          <t>Balance Drain</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -20265,103 +20245,103 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>UNDER_REVIEW</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-07-26 16:12</t>
+          <t>2026-07-27 18:27</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ALT20260726032303_055_e1cc</t>
+          <t>ALT20260727111050_101_96a7</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>TXN_20260726_00280_20ee31</t>
+          <t>TXN_20260727_02120_bb6ab9</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Balance Drain</t>
+          <t>Impossible Travel, Balance Drain, Very Large Transaction</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-07-26 03:23</t>
+          <t>2026-07-27 11:10</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ALT20260726015601_104_4266</t>
+          <t>ALT20260727110706_099_05a8</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>TXN_20260726_02240_270457</t>
+          <t>TXN_20260727_02040_7c6879</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>New Account Activity, Mule Account Activity, Large Transaction</t>
+          <t>Balance Drain</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>UNDER_REVIEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-07-26 01:56</t>
+          <t>2026-07-27 11:07</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ALT20260725175815_034_fca7</t>
+          <t>ALT20260726230032_054_4584</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>TXN_20260725_00034_4cb951</t>
+          <t>TXN_20260726_00240_31760a</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Rapid Transfers</t>
+          <t>Device Change, Mule Account Activity, Impossible Travel</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -20370,33 +20350,33 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>UNDER_REVIEW</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-07-25 17:58</t>
+          <t>2026-07-26 23:00</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ALT20260725164207_082_1f1d</t>
+          <t>ALT20260726170102_107_f3bc</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>TXN_20260725_01360_a61954</t>
+          <t>TXN_20260726_02360_eb7295</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Rapid Transfers, Large Transaction, Device Change</t>
+          <t>Impossible Travel, Device Change</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -20405,37 +20385,37 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-07-25 16:42</t>
+          <t>2026-07-26 17:01</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ALT20260725162402_068_0bfa</t>
+          <t>ALT20260726161233_019_5213</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>TXN_20260725_00800_ee2fea</t>
+          <t>TXN_20260726_00019_4433ff</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Very Large Transaction</t>
+          <t>Rapid Transfers, Balance Drain, Very Large Transaction</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -20445,32 +20425,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-07-25 16:24</t>
+          <t>2026-07-26 16:12</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ALT20260725082636_039_d819</t>
+          <t>ALT20260726032303_055_e1cc</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>TXN_20260725_00039_fb14f3</t>
+          <t>TXN_20260726_00280_20ee31</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Device Change, Very Large Transaction</t>
+          <t>Balance Drain</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -20480,32 +20460,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-07-25 08:26</t>
+          <t>2026-07-26 03:23</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ALT20260725051542_002_4d59</t>
+          <t>ALT20260726015601_104_4266</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>TXN_20260725_00002_e0dad2</t>
+          <t>TXN_20260726_02240_270457</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>New Account Activity, Impossible Travel, Large Transaction</t>
+          <t>New Account Activity, Mule Account Activity, Large Transaction</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -20515,28 +20495,28 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-07-25 05:15</t>
+          <t>2026-07-26 01:56</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ALT20260724214702_116_8026</t>
+          <t>ALT20260725175815_034_fca7</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>TXN_20260724_02720_739a45</t>
+          <t>TXN_20260725_00034_4cb951</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Balance Drain, Impossible Travel</t>
+          <t>Rapid Transfers</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -20550,28 +20530,28 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-07-24 21:47</t>
+          <t>2026-07-25 17:58</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ALT20260724200225_044_6bbe</t>
+          <t>ALT20260725164207_082_1f1d</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>TXN_20260724_00044_a0f518</t>
+          <t>TXN_20260725_01360_a61954</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Impossible Travel, Very Large Transaction, Rapid Transfers</t>
+          <t>Rapid Transfers, Large Transaction, Device Change</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -20585,28 +20565,28 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-07-24 20:02</t>
+          <t>2026-07-25 16:42</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ALT20260724142524_093_4d2d</t>
+          <t>ALT20260725162402_068_0bfa</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>TXN_20260724_01800_4f868f</t>
+          <t>TXN_20260725_00800_ee2fea</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Mule Account Activity</t>
+          <t>Very Large Transaction</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -20615,33 +20595,33 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-07-24 14:25</t>
+          <t>2026-07-25 16:24</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ALT20260724012524_076_c07d</t>
+          <t>ALT20260725082636_039_d819</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>TXN_20260724_01120_1bee46</t>
+          <t>TXN_20260725_00039_fb14f3</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Impossible Travel, Mule Account Activity, Device Change</t>
+          <t>Device Change, Very Large Transaction</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -20655,63 +20635,63 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-07-24 01:25</t>
+          <t>2026-07-25 08:26</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ALT20260723164334_050_f8cd</t>
+          <t>ALT20260725051542_002_4d59</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>TXN_20260723_00080_90b787</t>
+          <t>TXN_20260725_00002_e0dad2</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>New Account Activity</t>
+          <t>New Account Activity, Impossible Travel, Large Transaction</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>UNDER_REVIEW</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-07-23 16:43</t>
+          <t>2026-07-25 05:15</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ALT20260723034854_026_a7ce</t>
+          <t>ALT20260724214702_116_8026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>TXN_20260723_00026_16effe</t>
+          <t>TXN_20260724_02720_739a45</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Large Transaction</t>
+          <t>Balance Drain, Impossible Travel</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -20725,28 +20705,28 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-07-23 03:48</t>
+          <t>2026-07-24 21:47</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ALT20260722204400_113_64fa</t>
+          <t>ALT20260724200225_044_6bbe</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>TXN_20260722_02600_af1c89</t>
+          <t>TXN_20260724_00044_a0f518</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Device Change</t>
+          <t>Impossible Travel, Very Large Transaction, Rapid Transfers</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -20755,33 +20735,33 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>UNDER_REVIEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026-07-22 20:44</t>
+          <t>2026-07-24 20:02</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ALT20260722122013_096_fd28</t>
+          <t>ALT20260724142524_093_4d2d</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>TXN_20260722_01920_d72b57</t>
+          <t>TXN_20260724_01800_4f868f</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Mule Account Activity, Very Large Transaction</t>
+          <t>Mule Account Activity</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -20790,68 +20770,68 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>UNDER_REVIEW</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026-07-22 12:20</t>
+          <t>2026-07-24 14:25</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ALT20260721234013_105_5b6c</t>
+          <t>ALT20260724012524_076_c07d</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>TXN_20260721_02280_23382f</t>
+          <t>TXN_20260724_01120_1bee46</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Large Transaction, Rapid Transfers</t>
+          <t>Impossible Travel, Mule Account Activity, Device Change</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>UNDER_REVIEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026-07-21 23:40</t>
+          <t>2026-07-24 01:25</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ALT20260721131055_071_b211</t>
+          <t>ALT20260723164334_050_f8cd</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>TXN_20260721_00920_9ae3e7</t>
+          <t>TXN_20260723_00080_90b787</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Rapid Transfers, New Account Activity, Impossible Travel</t>
+          <t>New Account Activity</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -20860,33 +20840,33 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>UNDER_REVIEW</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026-07-21 13:10</t>
+          <t>2026-07-23 16:43</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ALT20260721111202_059_b13f</t>
+          <t>ALT20260723034854_026_a7ce</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>TXN_20260721_00440_239102</t>
+          <t>TXN_20260723_00026_16effe</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Impossible Travel</t>
+          <t>Large Transaction</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -20895,37 +20875,37 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>UNDER_REVIEW</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-07-21 11:12</t>
+          <t>2026-07-23 03:48</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ALT20260721103258_075_5492</t>
+          <t>ALT20260722204400_113_64fa</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>TXN_20260721_01080_05b350</t>
+          <t>TXN_20260722_02600_af1c89</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Rapid Transfers, Mule Account Activity</t>
+          <t>Device Change</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -20935,28 +20915,28 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-07-21 10:32</t>
+          <t>2026-07-22 20:44</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ALT20260721005505_073_7905</t>
+          <t>ALT20260722122013_096_fd28</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>TXN_20260721_01000_28fb8e</t>
+          <t>TXN_20260722_01920_d72b57</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>New Account Activity, Device Change, Balance Drain</t>
+          <t>Mule Account Activity, Very Large Transaction</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -20965,107 +20945,107 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>UNDER_REVIEW</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026-07-21 00:55</t>
+          <t>2026-07-22 12:20</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ALT20260720110916_085_8a16</t>
+          <t>ALT20260721234013_105_5b6c</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>TXN_20260720_01480_8a1076</t>
+          <t>TXN_20260721_02280_23382f</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Rapid Transfers</t>
+          <t>Large Transaction, Rapid Transfers</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>UNDER_REVIEW</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026-07-20 11:09</t>
+          <t>2026-07-21 23:40</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ALT20260719173051_095_2392</t>
+          <t>ALT20260721131055_071_b211</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>TXN_20260719_01880_d85353</t>
+          <t>TXN_20260721_00920_9ae3e7</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Very Large Transaction, Device Change</t>
+          <t>Rapid Transfers, New Account Activity, Impossible Travel</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>UNDER_REVIEW</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026-07-19 17:30</t>
+          <t>2026-07-21 13:10</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ALT20260719142028_046_e82e</t>
+          <t>ALT20260721111202_059_b13f</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>TXN_20260719_00046_4f028d</t>
+          <t>TXN_20260721_00440_239102</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>New Account Activity, Device Change, Rapid Transfers</t>
+          <t>Impossible Travel</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -21075,98 +21055,98 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-07-19 14:20</t>
+          <t>2026-07-21 11:12</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ALT20260719021853_090_beaa</t>
+          <t>ALT20260721103258_075_5492</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>TXN_20260719_01680_749f5f</t>
+          <t>TXN_20260721_01080_05b350</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Mule Account Activity, New Account Activity</t>
+          <t>Rapid Transfers, Mule Account Activity</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>UNDER_REVIEW</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-07-19 02:18</t>
+          <t>2026-07-21 10:32</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ALT20260718122032_065_6a46</t>
+          <t>ALT20260721005505_073_7905</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>TXN_20260718_00680_31b864</t>
+          <t>TXN_20260721_01000_28fb8e</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Large Transaction</t>
+          <t>New Account Activity, Device Change, Balance Drain</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>UNDER_REVIEW</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026-07-18 12:20</t>
+          <t>2026-07-21 00:55</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ALT20260718043856_088_b616</t>
+          <t>ALT20260720110916_085_8a16</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>TXN_20260718_01600_e11cde</t>
+          <t>TXN_20260720_01480_8a1076</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Balance Drain</t>
+          <t>Rapid Transfers</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -21180,98 +21160,98 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026-07-18 04:38</t>
+          <t>2026-07-20 11:09</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ALT20260717231228_115_5015</t>
+          <t>ALT20260719173051_095_2392</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>TXN_20260717_02680_509f44</t>
+          <t>TXN_20260719_01880_d85353</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Impossible Travel, New Account Activity</t>
+          <t>Very Large Transaction, Device Change</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026-07-17 23:12</t>
+          <t>2026-07-19 17:30</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ALT20260717142202_118_c806</t>
+          <t>ALT20260719142028_046_e82e</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>TXN_20260717_02800_70997e</t>
+          <t>TXN_20260719_00046_4f028d</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Impossible Travel</t>
+          <t>New Account Activity, Device Change, Rapid Transfers</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>UNDER_REVIEW</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026-07-17 14:22</t>
+          <t>2026-07-19 14:20</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ALT20260717061629_083_42a7</t>
+          <t>ALT20260719021853_090_beaa</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>TXN_20260717_01400_d80d87</t>
+          <t>TXN_20260719_01680_749f5f</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Large Transaction, Device Change, Very Large Transaction</t>
+          <t>Mule Account Activity, New Account Activity</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -21285,32 +21265,32 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026-07-17 06:16</t>
+          <t>2026-07-19 02:18</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ALT20260717043850_100_42d8</t>
+          <t>ALT20260718122032_065_6a46</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>TXN_20260717_02080_a4feba</t>
+          <t>TXN_20260718_00680_31b864</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Balance Drain, Large Transaction</t>
+          <t>Large Transaction</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -21320,102 +21300,102 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026-07-17 04:38</t>
+          <t>2026-07-18 12:20</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ALT20260716235258_023_ad64</t>
+          <t>ALT20260718043856_088_b616</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>TXN_20260716_00023_d96525</t>
+          <t>TXN_20260718_01600_e11cde</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Impossible Travel, Rapid Transfers</t>
+          <t>Balance Drain</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>UNDER_REVIEW</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026-07-16 23:52</t>
+          <t>2026-07-18 04:38</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ALT20260716141400_025_70eb</t>
+          <t>ALT20260717231228_115_5015</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>TXN_20260716_00025_54fa15</t>
+          <t>TXN_20260717_02680_509f44</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>New Account Activity, Very Large Transaction, Balance Drain</t>
+          <t>Impossible Travel, New Account Activity</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026-07-16 14:14</t>
+          <t>2026-07-17 23:12</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ALT20260716095749_022_5695</t>
+          <t>ALT20260717142202_118_c806</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>TXN_20260716_00022_ff321c</t>
+          <t>TXN_20260717_02800_70997e</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Rapid Transfers</t>
+          <t>Impossible Travel</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -21425,28 +21405,28 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026-07-16 09:57</t>
+          <t>2026-07-17 14:22</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ALT20260716061456_032_16ce</t>
+          <t>ALT20260717061629_083_42a7</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>TXN_20260716_00032_b07ea4</t>
+          <t>TXN_20260717_01400_d80d87</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Device Change, Balance Drain</t>
+          <t>Large Transaction, Device Change, Very Large Transaction</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -21455,107 +21435,107 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026-07-16 06:14</t>
+          <t>2026-07-17 06:16</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ALT20260715223650_051_5874</t>
+          <t>ALT20260717043850_100_42d8</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>TXN_20260715_00120_32d8d2</t>
+          <t>TXN_20260717_02080_a4feba</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Device Change, Rapid Transfers, Large Transaction</t>
+          <t>Balance Drain, Large Transaction</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>UNDER_REVIEW</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026-07-15 22:36</t>
+          <t>2026-07-17 04:38</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ALT20260715133137_033_c8d4</t>
+          <t>ALT20260716235258_023_ad64</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>TXN_20260715_00033_9720e1</t>
+          <t>TXN_20260716_00023_d96525</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Mule Account Activity</t>
+          <t>Impossible Travel, Rapid Transfers</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>UNDER_REVIEW</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026-07-15 13:31</t>
+          <t>2026-07-16 23:52</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ALT20260715045056_018_4b33</t>
+          <t>ALT20260716141400_025_70eb</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>TXN_20260715_00018_0ec6b1</t>
+          <t>TXN_20260716_00025_54fa15</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Mule Account Activity</t>
+          <t>New Account Activity, Very Large Transaction, Balance Drain</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -21565,32 +21545,32 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026-07-15 04:50</t>
+          <t>2026-07-16 14:14</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ALT20260715015242_064_99e7</t>
+          <t>ALT20260716095749_022_5695</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>TXN_20260715_00640_9122d3</t>
+          <t>TXN_20260716_00022_ff321c</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Mule Account Activity</t>
+          <t>Rapid Transfers</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -21600,28 +21580,28 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026-07-15 01:52</t>
+          <t>2026-07-16 09:57</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ALT20260714052029_036_378d</t>
+          <t>ALT20260716061456_032_16ce</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>TXN_20260714_00036_4f9dae</t>
+          <t>TXN_20260716_00032_b07ea4</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Large Transaction, Device Change</t>
+          <t>Device Change, Balance Drain</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -21630,68 +21610,68 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>UNDER_REVIEW</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026-07-14 05:20</t>
+          <t>2026-07-16 06:14</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>ALT20260713224951_012_3e4b</t>
+          <t>ALT20260715223650_051_5874</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>TXN_20260713_00012_5915a1</t>
+          <t>TXN_20260715_00120_32d8d2</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Large Transaction, Very Large Transaction, New Account Activity</t>
+          <t>Device Change, Rapid Transfers, Large Transaction</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>UNDER_REVIEW</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026-07-13 22:49</t>
+          <t>2026-07-15 22:36</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ALT20260713115531_080_90e4</t>
+          <t>ALT20260715133137_033_c8d4</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>TXN_20260713_01280_f55b6a</t>
+          <t>TXN_20260715_00033_9720e1</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Very Large Transaction, Impossible Travel, Device Change</t>
+          <t>Mule Account Activity</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -21700,103 +21680,103 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>UNDER_REVIEW</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2026-07-13 11:55</t>
+          <t>2026-07-15 13:31</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ALT20260713004451_058_a581</t>
+          <t>ALT20260715045056_018_4b33</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>TXN_20260713_00400_ebadc5</t>
+          <t>TXN_20260715_00018_0ec6b1</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Impossible Travel, Balance Drain, Large Transaction</t>
+          <t>Mule Account Activity</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2026-07-13 00:44</t>
+          <t>2026-07-15 04:50</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ALT20260712231240_043_413a</t>
+          <t>ALT20260715015242_064_99e7</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>TXN_20260712_00043_26c248</t>
+          <t>TXN_20260715_00640_9122d3</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Impossible Travel, Balance Drain, New Account Activity</t>
+          <t>Mule Account Activity</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>UNDER_REVIEW</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2026-07-12 23:12</t>
+          <t>2026-07-15 01:52</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ALT20260712191111_089_f499</t>
+          <t>ALT20260714052029_036_378d</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>TXN_20260712_01640_382fe2</t>
+          <t>TXN_20260714_00036_4f9dae</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Balance Drain</t>
+          <t>Large Transaction, Device Change</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -21805,33 +21785,33 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>UNDER_REVIEW</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2026-07-12 19:11</t>
+          <t>2026-07-14 05:20</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ALT20260712172332_112_0bea</t>
+          <t>ALT20260713224951_012_3e4b</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>TXN_20260712_02560_992fa5</t>
+          <t>TXN_20260713_00012_5915a1</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Impossible Travel, Device Change</t>
+          <t>Large Transaction, Very Large Transaction, New Account Activity</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -21840,45 +21820,220 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>UNDER_REVIEW</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2026-07-12 17:23</t>
+          <t>2026-07-13 22:49</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
+          <t>ALT20260713115531_080_90e4</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>TXN_20260713_01280_f55b6a</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Very Large Transaction, Impossible Travel, Device Change</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>95</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>UNDER_REVIEW</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>2026-07-13 11:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>ALT20260713004451_058_a581</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>TXN_20260713_00400_ebadc5</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Impossible Travel, Balance Drain, Large Transaction</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>91</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>2026-07-13 00:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>ALT20260712231240_043_413a</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>TXN_20260712_00043_26c248</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Impossible Travel, Balance Drain, New Account Activity</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>77</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>2026-07-12 23:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>ALT20260712191111_089_f499</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>TXN_20260712_01640_382fe2</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Balance Drain</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>94</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>2026-07-12 19:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>ALT20260712172332_112_0bea</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>TXN_20260712_02560_992fa5</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Impossible Travel, Device Change</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>88</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>2026-07-12 17:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
           <t>ALT20260712153853_081_930b</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr">
+      <c r="B141" t="inlineStr">
         <is>
           <t>TXN_20260712_01320_20d364</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr">
+      <c r="C141" t="inlineStr">
         <is>
           <t>Balance Drain, Large Transaction, Rapid Transfers</t>
         </is>
       </c>
-      <c r="D136" t="n">
+      <c r="D141" t="n">
         <v>93</v>
       </c>
-      <c r="E136" t="inlineStr">
+      <c r="E141" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr">
+      <c r="F141" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr">
+      <c r="G141" t="inlineStr">
         <is>
           <t>2026-07-12 15:38</t>
         </is>
@@ -21952,11 +22107,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ACC_RING_A</t>
+          <t>ACC43249524</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>46000</v>
+        <v>65000</v>
       </c>
       <c r="D2" t="n">
         <v>75</v>
